--- a/examples/Phytoplankton-Huisman-model/Steadyflow_60m_depth/LB-Huisman-conversion_with_flow.xlsx
+++ b/examples/Phytoplankton-Huisman-model/Steadyflow_60m_depth/LB-Huisman-conversion_with_flow.xlsx
@@ -1,21 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Dropbox/2-Recherche/Huisman-with-LB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Dropbox/2-Recherche/ch4-project/examples/Phytoplankton-Huisman-model/Steadyflow_60m_depth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C662D482-9402-524A-904D-B350A02F75D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E526A41-8456-6B46-BBCB-D9BCCEECFB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="460" windowWidth="28900" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5620" yWindow="460" windowWidth="28900" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - Conversion from Physi" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1984,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="19">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>7</v>
@@ -2002,7 +2011,7 @@
       </c>
       <c r="B6" s="20">
         <f>B5/B4</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>9</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="E6" s="16">
         <f>B6*3600</f>
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>13</v>
@@ -2031,7 +2040,7 @@
       </c>
       <c r="D7" s="24">
         <f>B7/B5</f>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>11</v>
@@ -2065,7 +2074,7 @@
       </c>
       <c r="D9" s="30">
         <f>B9/B6</f>
-        <v>5.5555555555555556E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="E9" s="31" t="s">
         <v>14</v>
@@ -2150,7 +2159,7 @@
       </c>
       <c r="D14" s="24">
         <f>B14/(B5*B5)</f>
-        <v>3.7499999999999995E-10</v>
+        <v>9.3749999999999986E-11</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="17"/>
@@ -2168,7 +2177,7 @@
       </c>
       <c r="D15" s="30">
         <f>B15*B5</f>
-        <v>4.0000000000000008E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="17"/>
@@ -2186,7 +2195,7 @@
       </c>
       <c r="D16" s="24">
         <f>B16/(B4/(B5*B5))</f>
-        <v>1.4000000000000004</v>
+        <v>5.6000000000000014</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="17"/>
@@ -2204,7 +2213,7 @@
       </c>
       <c r="D17" s="30">
         <f>B17/(B4/(B5*B5))</f>
-        <v>0.12000000000000002</v>
+        <v>0.48000000000000009</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="17"/>
@@ -2215,7 +2224,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="22">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C18" s="23" t="s">
         <v>27</v>
@@ -2229,7 +2238,7 @@
       <c r="A19" s="34"/>
       <c r="B19" s="22">
         <f>B18*0.0001</f>
-        <v>5.0000000000000001E-4</v>
+        <v>2E-3</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>28</v>
@@ -2252,7 +2261,7 @@
         <v>41</v>
       </c>
       <c r="B20" s="22">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>13</v>
@@ -2266,14 +2275,14 @@
       <c r="A21" s="34"/>
       <c r="B21" s="22">
         <f>B20/3600</f>
-        <v>3.4444444444444442E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="24">
         <f>B21/B6</f>
-        <v>1.7222222222222222E-2</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="E21" s="36" t="s">
         <v>42</v>
@@ -2336,7 +2345,7 @@
       </c>
       <c r="D25" s="43">
         <f>B25*B5*B5*B5</f>
-        <v>8.0000000000000019E-3</v>
+        <v>6.4000000000000015E-2</v>
       </c>
       <c r="E25" s="44"/>
       <c r="F25" s="45"/>
@@ -2359,7 +2368,7 @@
       </c>
       <c r="B27" s="20">
         <f>D7</f>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -2387,7 +2396,7 @@
       </c>
       <c r="B29" s="20">
         <f>D21</f>
-        <v>1.7222222222222222E-2</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -2415,7 +2424,7 @@
       </c>
       <c r="B31" s="20">
         <f>D9</f>
-        <v>5.5555555555555556E-4</v>
+        <v>2.7777777777777778E-4</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
@@ -2457,7 +2466,7 @@
       </c>
       <c r="B34" s="20">
         <f>D17</f>
-        <v>0.12000000000000002</v>
+        <v>0.48000000000000009</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -2471,7 +2480,7 @@
       </c>
       <c r="B35" s="20">
         <f>D15</f>
-        <v>4.0000000000000008E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -2485,7 +2494,7 @@
       </c>
       <c r="B36" s="20">
         <f>D14</f>
-        <v>3.7499999999999995E-10</v>
+        <v>9.3749999999999986E-11</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
@@ -2499,7 +2508,7 @@
       </c>
       <c r="B37" s="20">
         <f>D16</f>
-        <v>1.4000000000000004</v>
+        <v>5.6000000000000014</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
